--- a/DataTables/DetailText/剧情/027_上元灯节.xlsx
+++ b/DataTables/DetailText/剧情/027_上元灯节.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5026D055-70F3-43E4-B7B4-F22517AE2311}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51D4C793-D096-45EB-930D-D1606D5960D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20085" yWindow="5055" windowWidth="16050" windowHeight="8025" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story" sheetId="3" r:id="rId1"/>
@@ -695,6 +695,259 @@
         <family val="2"/>
         <charset val="134"/>
       </rPr>
+      <t>东</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>璧，芷</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>兰</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>，咱</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>们去小摊儿</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>坐会儿吃点元宵。</t>
+    </r>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <r>
+      <t>res://Assets/Background/0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>27</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>027_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>.png</t>
+    </r>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <r>
+      <t>干了一年坐堂医，感</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>觉</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>怎么</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>样</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>，和你之前想的一</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>样吗？</t>
+    </r>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <r>
+      <t>我倒是挺喜</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>欢这</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>一行，只是</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>赚不到什么钱，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>苦了您和</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>芷兰了…</t>
+    </r>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>只要咱们一家人能一起平平安安的过日子，我就知足了，要那么多钱做什么。</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>是啊，一家人平平安安就好啊。</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>好了，不早了，咱们该回家了。</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
       <t>这</t>
     </r>
     <r>
@@ -705,261 +958,8 @@
         <family val="3"/>
         <charset val="128"/>
       </rPr>
-      <t>个我会，是"忍冬。</t>
-    </r>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>东</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>璧，芷</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>兰</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>，咱</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>们去小摊儿</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>坐会儿吃点元宵。</t>
-    </r>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <r>
-      <t>res://Assets/Background/0</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>27</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>027_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>0</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>5</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>.png</t>
-    </r>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <r>
-      <t>干了一年坐堂医，感</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>觉</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>怎么</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>样</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>，和你之前想的一</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>样吗？</t>
-    </r>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <r>
-      <t>我倒是挺喜</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>欢这</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>一行，只是</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>赚不到什么钱，</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>苦了您和</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>芷兰了…</t>
-    </r>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <t>只要咱们一家人能一起平平安安的过日子，我就知足了，要那么多钱做什么。</t>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <t>是啊，一家人平平安安就好啊。</t>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <t>好了，不早了，咱们该回家了。</t>
+      <t>个我会，是"忍冬"。</t>
+    </r>
     <phoneticPr fontId="4"/>
   </si>
 </sst>
@@ -2277,7 +2277,7 @@
       <c r="F23" s="3"/>
       <c r="G23" s="3"/>
       <c r="H23" s="31" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="I23" s="3"/>
     </row>
@@ -2298,7 +2298,7 @@
       <c r="F24" s="3"/>
       <c r="G24" s="3"/>
       <c r="H24" s="31" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="I24" s="3"/>
     </row>
@@ -2318,10 +2318,10 @@
       <c r="E25" s="3"/>
       <c r="F25" s="3"/>
       <c r="G25" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="H25" s="3" t="s">
         <v>72</v>
-      </c>
-      <c r="H25" s="3" t="s">
-        <v>73</v>
       </c>
       <c r="I25" s="3"/>
     </row>
@@ -2342,7 +2342,7 @@
       <c r="F26" s="3"/>
       <c r="G26" s="3"/>
       <c r="H26" s="3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="I26" s="3"/>
     </row>
@@ -2363,7 +2363,7 @@
       <c r="F27" s="3"/>
       <c r="G27" s="3"/>
       <c r="H27" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="I27" s="3"/>
     </row>
@@ -2384,7 +2384,7 @@
       <c r="F28" s="3"/>
       <c r="G28" s="3"/>
       <c r="H28" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="I28" s="3"/>
     </row>
@@ -2405,7 +2405,7 @@
       <c r="F29" s="3"/>
       <c r="G29" s="3"/>
       <c r="H29" s="3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="I29" s="3"/>
     </row>

--- a/DataTables/DetailText/剧情/027_上元灯节.xlsx
+++ b/DataTables/DetailText/剧情/027_上元灯节.xlsx
@@ -1,40 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51D4C793-D096-45EB-930D-D1606D5960D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{526E89B7-D6DF-4DF3-9513-E2226FE48F84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story" sheetId="3" r:id="rId1"/>
     <sheet name="StoryLine" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="79">
   <si>
     <t>LineIndex</t>
   </si>
@@ -960,6 +947,10 @@
       </rPr>
       <t>个我会，是"忍冬"。</t>
     </r>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>res://Assets/Music/Story/027/元宵夜樂.mp3</t>
     <phoneticPr fontId="4"/>
   </si>
 </sst>
@@ -1202,7 +1193,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="標準" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1413,7 +1404,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:T20"/>
-  <sheetFormatPr defaultRowHeight="18.75"/>
+  <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="6.75" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="9.25" bestFit="1" customWidth="1"/>
@@ -1431,7 +1422,7 @@
     <col min="19" max="20" width="10.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" s="21" customFormat="1" ht="18">
+    <row r="1" spans="1:20" s="21" customFormat="1">
       <c r="A1" s="16" t="s">
         <v>13</v>
       </c>
@@ -1493,7 +1484,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:20" s="21" customFormat="1" ht="18">
+    <row r="2" spans="1:20" s="21" customFormat="1">
       <c r="A2" s="25" t="s">
         <v>32</v>
       </c>
@@ -1826,7 +1817,9 @@
       <c r="H2" s="28" t="s">
         <v>38</v>
       </c>
-      <c r="I2" s="1"/>
+      <c r="I2" s="2" t="s">
+        <v>78</v>
+      </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="1">
